--- a/histograms/histogram_frac_d_valence_electrons.xlsx
+++ b/histograms/histogram_frac_d_valence_electrons.xlsx
@@ -445,7 +445,7 @@
         <v>0.02619010335108049</v>
       </c>
       <c r="B2" t="n">
-        <v>682</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>0.03973535859693079</v>
       </c>
       <c r="B3" t="n">
-        <v>2320</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>0.05328061384278109</v>
       </c>
       <c r="B4" t="n">
-        <v>2495</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>0.06682586908863139</v>
       </c>
       <c r="B5" t="n">
-        <v>1695</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>0.08037112433448168</v>
       </c>
       <c r="B6" t="n">
-        <v>1505</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>0.093916379580332</v>
       </c>
       <c r="B7" t="n">
-        <v>2700</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>0.1074616348261823</v>
       </c>
       <c r="B8" t="n">
-        <v>2540</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>0.1210068900720326</v>
       </c>
       <c r="B9" t="n">
-        <v>2348</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>0.1345521453178829</v>
       </c>
       <c r="B10" t="n">
-        <v>614</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>0.1480974005637332</v>
       </c>
       <c r="B11" t="n">
-        <v>4638</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>0.1616426558095835</v>
       </c>
       <c r="B12" t="n">
-        <v>988</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>0.1751879110554338</v>
       </c>
       <c r="B13" t="n">
-        <v>1273</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>0.1887331663012841</v>
       </c>
       <c r="B14" t="n">
-        <v>261</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>0.2022784215471344</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>0.2158236767929847</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>0.229368932038835</v>
       </c>
       <c r="B17" t="n">
-        <v>649</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>0.2429141872846853</v>
       </c>
       <c r="B18" t="n">
-        <v>743</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>0.2564594425305355</v>
       </c>
       <c r="B19" t="n">
-        <v>518</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>0.2700046977763859</v>
       </c>
       <c r="B20" t="n">
-        <v>223</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>0.2835499530222362</v>
       </c>
       <c r="B21" t="n">
-        <v>179</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
